--- a/test-data/Templates/DEV/R1.xlsx
+++ b/test-data/Templates/DEV/R1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejavathidoddapaneni/MaextroAutomationTests/test-data/Templates/DEV/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejavathidoddapaneni/Maextro_AutomationApp/test-data/Templates/DEV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77297470-7EEF-AC44-AC48-55327ACD8258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE27768-7828-6F4D-B256-020BB9F06CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
+    <workbookView xWindow="-20" yWindow="680" windowWidth="15140" windowHeight="17180" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
   </bookViews>
   <sheets>
     <sheet name="MXT_HDR" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="197">
   <si>
     <t>Object</t>
   </si>
@@ -626,19 +626,16 @@
     <t>View - QM</t>
   </si>
   <si>
-    <t>Skip</t>
-  </si>
-  <si>
     <t>AutoTestMat7</t>
   </si>
   <si>
     <t>AutoTestMat7 Desc</t>
   </si>
   <si>
-    <t>Reject -&gt; Approve</t>
-  </si>
-  <si>
     <t>Rejecting To</t>
+  </si>
+  <si>
+    <t>Approve</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1057,7 @@
     <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5" customWidth="1"/>
     <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.33203125" bestFit="1" customWidth="1"/>
@@ -1130,7 +1127,7 @@
         <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1160,7 +1157,7 @@
         <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>193</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -1174,7 +1171,7 @@
         <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>193</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -1188,7 +1185,7 @@
         <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>193</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -1202,7 +1199,7 @@
         <v>135</v>
       </c>
       <c r="D10" t="s">
-        <v>193</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -1216,7 +1213,7 @@
         <v>166</v>
       </c>
       <c r="D11" t="s">
-        <v>193</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -1230,7 +1227,7 @@
         <v>171</v>
       </c>
       <c r="D12" t="s">
-        <v>193</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1244,7 +1241,7 @@
         <v>180</v>
       </c>
       <c r="D13" t="s">
-        <v>193</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -1268,6 +1265,20 @@
       <c r="G23" s="8"/>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D6:D11 D13:D14 D12" xr:uid="{58227CB0-C6D9-A247-A15C-D0FCE8718EAF}">
+      <formula1>"Save,Skip,Approve,Reject -&gt; Approve"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{480D1B17-2E92-9240-8BCE-1DA3147CCDB2}">
+      <formula1>"Create New Material,Create Sales Pricing,New Sales Condition record,Create Purchase Order,Create Purchase requisition,Create Production Version,Habasit training"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{658924D3-9CAD-7045-B512-41FCE5F6FC9E}">
+      <formula1>"BSX RDS DIVISION,DEMO DIVISION CODE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{867B6D3F-F6EA-6D45-89A3-70B9CE3A4229}">
+      <formula1>"Low,Medium,High"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2186,10 +2197,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" t="s">
         <v>194</v>
-      </c>
-      <c r="C3" t="s">
-        <v>195</v>
       </c>
       <c r="D3" t="s">
         <v>42</v>
